--- a/docs/官方规则总表.xlsx
+++ b/docs/官方规则总表.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>error（2026-08-22 按确认口径）</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>未路由</t>
+          <t>完整设计图,竣工图,竣工图（含BOM）,设计图（含纤芯）</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
